--- a/Employee_Reports_wi52/Rogelio Reyes Gomez Jr. Q0301.xlsx
+++ b/Employee_Reports_wi52/Rogelio Reyes Gomez Jr. Q0301.xlsx
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-229</v>
+        <v>-237</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -630,11 +630,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-136</v>
+        <v>-144</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -679,11 +679,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-123</v>
+        <v>-131</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -728,11 +728,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-135</v>
+        <v>-143</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -777,11 +777,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-119</v>
+        <v>-127</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -826,11 +826,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -875,11 +875,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-123</v>
+        <v>-131</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -924,11 +924,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-118</v>
+        <v>-126</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-105</v>
+        <v>-113</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-124</v>
+        <v>-132</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1071,11 +1071,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-129</v>
+        <v>-137</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1120,11 +1120,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-107</v>
+        <v>-115</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1169,11 +1169,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1218,11 +1218,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1267,11 +1267,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1316,11 +1316,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1365,11 +1365,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1414,11 +1414,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1463,11 +1463,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1512,11 +1512,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1561,11 +1561,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1659,11 +1659,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1708,11 +1708,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1757,11 +1757,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1806,11 +1806,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1904,11 +1904,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2002,11 +2002,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2051,11 +2051,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2100,11 +2100,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2149,11 +2149,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2198,11 +2198,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2235,11 +2235,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2272,11 +2272,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
